--- a/assets/Support_Units.xlsx
+++ b/assets/Support_Units.xlsx
@@ -467,16 +467,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -502,21 +501,16 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Passive Amount</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>Active Cost</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Tails</t>
@@ -532,22 +526,19 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Draw a card at the end of your turn</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+          <t>Draw 1 card at the end of your turn (if not exhausted)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Play 1 card from your discard pile</t>
         </is>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Knuckles</t>
@@ -563,22 +554,19 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>+1 to Leader's Attack</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
+          <t>+1 to your Leader's attack</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Deal 1 damage to 1 opponent bench unit</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Deal 1 damage to one of your opponent's support units</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+    </row>
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Amy</t>
@@ -594,22 +582,19 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>+1 to Leader's Attack</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
+          <t>+1 to your Leader's attack</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Deal 1 damage to the opponent's Leader</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Deal 1 damage to your opponent's leader</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
+    </row>
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Cream</t>
@@ -625,22 +610,19 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Decrease Leader's Damage Taken</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
+          <t>Your Leader takes 1 less damage from attacks</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Heal 1 HP from any friendly unit (cannot exceed max HP)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Heal 1 HP from any friendly unit (cannot exceed max HP)</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
+    </row>
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Big</t>
@@ -656,22 +638,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Look at the top card of your deck and discard it if you'd like. If not, put it back at the top of your deck.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Discard a random card from your opponent's hand and place it into your discard pile.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n">
+          <t>Start of turn: look at top deck card, may discard it or put it back</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Discard a random card from opponent's hand</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Silver</t>
@@ -682,27 +661,24 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Aggro</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Friendly unit actives do not exhaust their unit — Silver exhausts instead when his active is used.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Deal 1 damage to the opponent's Leader for each unit active used this turn (including this one). Silver exhausts.</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
+          <t>All friendly unit actives cost 1 less energy (minimum 1)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Return one of your bench units to your hand. Scry 2: put 1 in your hand and 1 on the bottom of your deck.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Shadow</t>
@@ -718,22 +694,19 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Your Leader's base damage is 2 instead of 1.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Deal 3 damage to the opponent's Leader. Your Leader takes 2 unblockable, unreducible damage.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
+          <t>Your Leader's base damage is 2 instead of 1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Deal 3 damage to opponent's Leader. Your Leader takes 2 unblockable damage.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Mighty</t>
@@ -749,22 +722,19 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>After your Leader attacks, if damage dealt was 3 or higher, draw 1 card.</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Your Leader attacks a second time this turn with full target selection. Mighty exhausts.</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n">
+          <t>After your Leader deals 3 or more damage, draw 1 card</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Your Leader attacks a second time this turn. Mighty exhausts.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Rouge</t>
@@ -780,22 +750,19 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>When a card moves from your hand or deck into your discard, draw 1 card.</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Place the top card of your deck directly into your discard pile. Rouge does NOT exhaust.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n">
+          <t>When a card is milled from the top of your deck to your discard, draw 1 card</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Mill the top card of your deck to your discard. Does not exhaust. Once per turn.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Blaze</t>
@@ -811,22 +778,19 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>At the end of your turn, if your discard pile has 5 or more cards, heal your Leader 1 HP.</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Shuffle your entire discard pile back into your deck, then draw 2 cards. Blaze exhausts.</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n">
+          <t>End of turn: if your discard has 5+ cards, heal your Leader 1 HP</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Shuffle entire discard into deck, draw 2. Blaze exhausts.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1">
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Ray</t>
@@ -842,22 +806,19 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>When you play a card from your discard pile, draw 1 card.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Look at the top 3 cards of your deck — place 1 directly into your discard, return the rest in any order.</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="n">
+          <t>When you play a card from your discard, draw 1 card</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Look at top 3 deck cards — place 1 into discard, return rest in any order</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Charmy</t>
@@ -873,22 +834,19 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Each equipment card played this turn after the first costs 1 less energy (minimum 0).</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Draw 1 card for each equipment card played this turn.</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n">
+          <t>Each equipment card played this turn after the first costs 1 less energy (min 0)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Draw 1 card per equipment card played this turn</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Espio</t>
@@ -904,22 +862,19 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>After your Draw Phase: draw 1 extra card for each equipment card in your discard pile (maximum 2 extra).</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Shuffle up to 3 equipment cards from your discard pile back into your deck, then draw 1 card.</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
+          <t>After Draw Phase: draw 1 extra per equipment in your discard (max 2)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Shuffle up to 3 equipment from your discard back into deck, draw 1</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="15" ht="40" customHeight="1">
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Vector</t>
@@ -935,50 +890,16 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Each time your Leader takes damage this turn, draw 1 card.</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Deal damage equal to the total energy spent this turn, including this active's cost.</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n">
+          <t>Each time your Leader takes damage this turn, draw 1 card</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Deal damage equal to total energy spent this turn including this cost</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Omega</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>No passive.</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Choose one opponent bench unit — it stays exhausted until the start of YOUR next turn, ignoring their End Phase recovery.</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/assets/Support_Units.xlsx
+++ b/assets/Support_Units.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support Units" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50,12 +50,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F7"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -85,22 +85,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,18 +461,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
@@ -486,25 +482,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Archetype</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Active Cost</t>
         </is>
@@ -516,53 +522,73 @@
           <t>Tails</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>tails</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Draw 1 card at end of turn.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Play 1 card from your discard pile. Card shuffles back into your deck after use.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Draw 1 card at the end of your turn (if not exhausted)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Play 1 card from your discard pile</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Knuckles</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>knuckles</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>+1 to your Leader's attack</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Deal 1 damage to 1 opponent bench unit</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>+10 to Leader Attack.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Deal 10 damage to 1 opponent Support Unit.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -572,53 +598,73 @@
           <t>Amy</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>3</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>amy</t>
+        </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>+1 to your Leader's attack</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Deal 1 damage to the opponent's Leader</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>+10 to Leader Attack.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Deal 10 damage to opponent's Leader.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Cream</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>cream</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Your Leader takes 1 less damage from attacks</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Heal 1 HP from any friendly unit (cannot exceed max HP)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>-10 to damage taken by Leader.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Heal 10 HP from any friendly unit (cannot exceed max HP).</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -628,53 +674,73 @@
           <t>Big</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>4</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>big</t>
+        </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Start of turn: look at top deck card, may discard it or put it back</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Discard a random card from opponent's hand</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Start of turn: look at top deck card, may discard it.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Discard a random card from opponent's hand.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>All friendly unit actives cost 1 less energy (minimum 1)</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Return one of your bench units to your hand. Scry 2: put 1 in your hand and 1 on the bottom of your deck.</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>All friendly unit actives cost 1 less energy (minimum 1).</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Return one of your bench units to your hand (unit active resets).</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -684,53 +750,73 @@
           <t>Shadow</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>4</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>shadow</t>
+        </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Your Leader's base damage is 2 instead of 1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Deal 3 damage to opponent's Leader. Your Leader takes 2 unblockable damage.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>3</v>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>While on bench: double your Leader's base damage. Stacks per Shadow.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Both Leaders take 10 unblockable, unreducible damage.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Mighty</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>mighty</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>After your Leader deals 3 or more damage, draw 1 card</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Your Leader attacks a second time this turn. Mighty exhausts.</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>After your Leader attacks, if damage dealt was 30 or higher, draw 1 card.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Your Leader attacks a second time this turn. Opponent may block.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -740,53 +826,73 @@
           <t>Rouge</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>2</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>rouge</t>
+        </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>When a card is milled from the top of your deck to your discard, draw 1 card</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Mill the top card of your deck to your discard. Does not exhaust. Once per turn.</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>When a card is milled from deck to discard, draw 1 card.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Place the top card of your deck directly into your discard pile. Rouge does NOT exhaust.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Blaze</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>blaze</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>End of turn: if your discard has 5+ cards, heal your Leader 1 HP</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Shuffle entire discard into deck, draw 2. Blaze exhausts.</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>At end of turn, if discard pile has 5+ cards, heal Leader 10 HP.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Shuffle your entire discard pile back into your deck, then draw 2 cards. Blaze exhausts.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -796,53 +902,73 @@
           <t>Ray</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>4</v>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ray</t>
+        </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>When you play a card from your discard, draw 1 card</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Look at top 3 deck cards — place 1 into discard, return rest in any order</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>When you play a card from your discard pile, draw 1 card.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Look at the top 3 cards of your deck — place 1 directly into your discard, return the rest in any order.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Charmy</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>charmy</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Rings</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Each equipment card played this turn after the first costs 1 less energy (min 0)</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Draw 1 card per equipment card played this turn</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Each equipment card played this turn after the first costs 1 less energy (minimum 0).</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Draw 1 card for each equipment card played this turn.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -852,56 +978,647 @@
           <t>Espio</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>espio</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Rings</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>After your Draw Phase: draw 1 extra card for each equipment card in your discard (max 2 extra).</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Shuffle up to 3 equipment cards from your discard back into your deck, then draw 1.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>vector</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Rings</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Each time your Leader takes damage this turn, draw 1 card.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Deal damage equal to the total energy spent this turn (×10, including this active's cost).</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Rings</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>After Draw Phase: draw 1 extra per equipment in your discard (max 2)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Shuffle up to 3 equipment from your discard back into deck, draw 1</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Caroline</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>caroline</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>If Justine is on bench, gain: (3E) The opponent can only play 1 equipment card this turn.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>If Justine was sent from the bench to the discard alone on your previous turn, revive her to your bench.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Justine</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>justine</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>If Caroline is on bench, gain: (2E) Disable an enemy active until your next turn.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>If Caroline was sent from the bench to the discard alone on your previous turn, revive her to your bench.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Rings</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Each time your Leader takes damage this turn, draw 1 card</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Deal damage equal to total energy spent this turn including this cost</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Tae Takumi</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>tae_takumi</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Your leader gains -10 damage taken during your opponent's turn.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Heal your leader for 20 HP (cannot exceed max HP).</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Sojiro Sakura</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>sojiro_sakura</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Your leader gains -10 damage taken during your opponent's turn.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Gain taunt until your next turn (opponent must attack this unit first if able).</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sae Niijima</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>sae_niijima</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Your opponent's Elemental Shield / damage reduction effects are reduced by 10.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Your next Leader attack this turn cannot be blocked.</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Sadayo Kawakami</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>sadayo_kawakami</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>+10 to Leader Attack.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Deal 10 damage to each support unit on the opponent's bench.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Suguru Kamoshida</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>suguru_kamoshida</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>When damage is dealt to the opposing leader this turn, they discard 1 card at random.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Your opponent discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ryuji Sakamoto</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ryuji_sakamoto</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>After your Leader attacks, if damage dealt was 20 or higher, your leader heals 10 HP.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Deal 10 damage to your opponent's leader.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Ann Takamaki</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>ann_takamaki</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Whenever the opponent discards a card, deal 10 damage to their leader.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Exile a card from the opponent's discard for each card they discarded this turn.</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Morgana</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>morgana</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>No passive.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Morgana and one enemy benched support unit are both sent to the discard.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Yusuke Kitagawa</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>yusuke_kitagawa</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>When Yusuke is placed on the bench, copy a passive ability from any benched support unit.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Copy and activate any friendly supporter's active ability.</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Makoto Niijima</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>makoto_niijima</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>After your Leader attacks, if damage dealt was 20 or higher, your leader heals 10 HP.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Deal damage to the opposing leader equal to total HP healed this turn.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Futaba Sakura</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>futaba_sakura</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>You may scry 1 at the end of each turn.</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Draw cards equal to total damage dealt to enemy units this turn.</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Haru Okumura</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>haru_okumura</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Haru cannot be targeted by opposing damage or abilities unless it is a direct Leader attack.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Prevent all damage to your leader until your next turn. Haru stays exhausted until the end of your next turn.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sumire Yoshizawa</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>sumire_yoshizawa</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Whenever the opponent discards a card, deal 10 damage to their leader.</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Deal 20 damage to one opposing benched supporter. Cannot be blocked.</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/Support_Units.xlsx
+++ b/assets/Support_Units.xlsx
@@ -10,7 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sonic IP Units" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Persona 5 IP Units" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sonic IP Units'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Persona 5 IP Units'!$A$1:$G$16</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,125 +21,118 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
+      <b val="1"/>
+      <color rgb="001A8EFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A8EFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0000CC44"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00E8F0FF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FFD700"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF2244"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00FF66CC"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="10"/>
+      <color rgb="00FF66CC"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00CC44FF"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="5">
     <fill>
-      <patternFill patternType="solid"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
+        <fgColor rgb="000066CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="000D2040"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF2F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="000A1A2E"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
-      <left>
-        <color rgb="FF000000"/>
-      </left>
-      <right>
-        <color rgb="FF000000"/>
-      </right>
-      <top>
-        <color rgb="FF000000"/>
-      </top>
-      <bottom>
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal>
-        <color rgb="FF000000"/>
-      </diagonal>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="001A3A5E"/>
       </left>
       <right style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="001A3A5E"/>
       </right>
       <top style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="001A3A5E"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="001A3A5E"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,95 +140,134 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -524,447 +559,523 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000D2040"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Archetype</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Passive Ability</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Active Ability</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Active Cost</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Tails</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Draw 1 card at the end of your turn (does not trigger if Tails is exhausted).</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Play 1 card from your discard pile (shuffles back into deck after use).</t>
         </is>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="G2" s="7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
+    <row r="3" ht="52" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Knuckles</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>+10 to Leader's Attack.</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Deal 10 damage to 1 opponent Support Unit.</t>
         </is>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="G3" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Amy</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>+10 to Leader's Attack.</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Deal 10 damage to opponent's Leader.</t>
         </is>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="52" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Cream</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>-10 to damage taken by Leader (always active).</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Heal 10 HP from any friendly unit (cannot exceed max HP).</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="G5" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Big</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Start of turn: look at top card of your deck; you may discard it or put it back.</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Start of turn: look at the top card of your deck; you may discard it or put it back. Skipped if deck is empty.</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Discard a random card from opponent's hand.</t>
         </is>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="7" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="52" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Rings</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>All friendly unit actives cost 1 less energy (minimum 1).</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Return one of your bench units to your hand (active resets).</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="G7" s="14" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Shadow</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Your Leader's base damage is doubled while Shadow is on bench (stacks per Shadow).</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Your Leader's base damage is doubled while Shadow is on bench (stacks per Shadow on bench).</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Both Leaders take 10 unblockable, unreducible damage.</t>
         </is>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Mighty</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>After your Leader attacks, if damage dealt was 30 or higher, draw 1 card.</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Your Leader attacks a second time this turn. Opponent may block.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="G9" s="14" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Rouge</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>When a card is milled from your deck to your discard, draw 1 card.</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Place the top card of your deck into your discard pile. Rouge does NOT exhaust.</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Blaze</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>End of turn: if your discard has 5+ cards, heal your Leader 10 HP.</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Shuffle your entire discard pile back into your deck, then draw 2 cards. Blaze exhausts.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="G11" s="14" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Ray</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>When you play a card from your discard pile, draw 1 card.</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Look at top 3 deck cards — place 1 into your discard, return the rest in any order.</t>
         </is>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="G12" s="7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="52" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Charmy</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Rings</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Each equipment card played this turn after the first costs 1 less energy (minimum 0).</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Draw 1 card for each equipment card played this turn.</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="G13" s="14" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Espio</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Rings</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>After your Draw Phase: draw 1 extra card for each equipment in your discard (max 2 extra).</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>After your Draw Phase: draw 1 extra card for each equipment card in your discard (max 2 extra).</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Shuffle up to 3 equipment cards from your discard back into your deck, then draw 1.</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="15" ht="40" customHeight="1">
+    <row r="15" ht="52" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Rings</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Each time your Leader takes damage this turn, draw 1 card.</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Deal damage equal to total energy spent this turn ×10 (including this active's cost).</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="G15" s="14" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="16" ht="40" customHeight="1"/>
   </sheetData>
+  <autoFilter ref="A1:G15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -972,473 +1083,556 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002A0D20"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Archetype</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Passive Ability</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Active Ability</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Active Cost</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Caroline</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>If Justine is on bench: opponent can only play 1 equipment card this turn.</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>If Justine was KO'd alone last turn, revive her to your bench.</t>
         </is>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="G2" s="7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3" ht="52" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Justine</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>If Caroline is on bench: disable one enemy active until your next turn.</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>If Caroline is on bench: disable one enemy active ability until your next turn.</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>If Caroline was KO'd alone last turn, revive her to your bench.</t>
         </is>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="G3" s="14" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Tae Takumi</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Your leader takes -10 damage during opponent's turn.</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Heal your leader for 20 HP (cannot exceed max HP).</t>
         </is>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Sojiro Sakura</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Your leader takes -10 damage during opponent's turn.</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Gain taunt until your next turn (opponent must attack this unit first if able).</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Sae Niijima</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Opponent's damage reduction effects are reduced by 10.</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Your next Leader attack this turn cannot be blocked.</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Sadayo Kawakami</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>+10 to Leader's Attack.</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Deal 10 damage to each support unit on the opponent's bench.</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Suguru Kamoshida</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>When damage is dealt to the opposing leader this turn, they discard 1 card at random.</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Your opponent discards 2 cards at random.</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Ryuji Sakamoto</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>After your Leader attacks, if damage dealt was 20 or higher, your leader heals 10 HP.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Deal 10 damage to your opponent's leader.</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Ann Takamaki</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Whenever the opponent discards a card, deal 10 damage to their leader.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Exile a card from the opponent's discard for each card they discarded this turn.</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Morgana</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>No passive.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Morgana and one enemy benched support unit are both sent to the discard.</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Yusuke Kitagawa</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>When Yusuke is placed on the bench, copy a passive from any benched support unit.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Copy and activate any friendly supporter's active ability.</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Makoto Niijima</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>After your Leader attacks, if damage dealt was 20 or higher, your leader heals 10 HP.</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Deal damage to the opposing leader equal to total HP healed this turn.</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Futaba Sakura</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>You may scry 1 at the end of each turn.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Draw cards equal to total damage dealt to enemy units this turn.</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Haru Okumura</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Your leader takes -10 damage during opponent's turn.</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Gain taunt until your next turn (opponent must attack this unit first if able).</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n">
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Haru cannot be targeted by opposing damage or abilities (only direct Leader attacks bypass this).</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Prevent all damage to your leader until your next turn. Haru stays exhausted until end of your next turn.</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Sae Niijima</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Sumire Yoshizawa</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>Aggro</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Opponent's damage reduction effects are reduced by 10.</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Your next Leader attack this turn cannot be blocked.</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sadayo Kawakami</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Aggro</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>+10 to Leader's Attack.</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Deal 10 damage to each support unit on the opponent's bench.</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Suguru Kamoshida</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Aggro</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>When damage is dealt to the opposing leader this turn, they discard 1 card at random.</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Your opponent discards 2 cards at random.</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Whenever the opponent discards a card, deal 10 damage to their leader.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Deal 20 unblockable damage to one opposing benched supporter.</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Ryuji Sakamoto</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Aggro</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>After your Leader attacks, if damage dealt was 20 or higher, your leader heals 10 HP.</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Deal 10 damage to your opponent's leader.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Ann Takamaki</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Whenever the opponent discards a card, deal 10 damage to their leader.</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Exile a card from the opponent's discard for each card they discarded this turn.</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Morgana</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>No passive.</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Morgana and one enemy benched support unit are both sent to the discard.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Yusuke Kitagawa</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>When Yusuke is placed on the bench, copy a passive from any benched support unit.</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Copy and activate any friendly supporter's active ability.</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Makoto Niijima</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Aggro</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>After your Leader attacks, if damage dealt was 20 or higher, your leader heals 10 HP.</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Deal damage to the opposing leader equal to total HP healed this turn.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Futaba Sakura</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>You may scry 1 at the end of each turn.</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Draw cards equal to total damage dealt to enemy units this turn.</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Haru Okumura</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Haru cannot be targeted by opposing damage or abilities (only direct Leader attacks bypass this).</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Prevent all damage to your leader until your next turn. Haru stays exhausted until end of your next turn.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Sumire Yoshizawa</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Aggro</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Whenever the opponent discards a card, deal 10 damage to their leader.</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Deal 20 unblockable damage to one opposing benched supporter.</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:G16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>